--- a/excel/output_stats_sfvv/covariance/EfficiencyStats.xlsx
+++ b/excel/output_stats_sfvv/covariance/EfficiencyStats.xlsx
@@ -499,16 +499,16 @@
         <v>42.6729</v>
       </c>
       <c r="F2" t="n">
-        <v>354.79</v>
+        <v>355.89</v>
       </c>
       <c r="G2" t="n">
-        <v>357.83</v>
+        <v>359.16</v>
       </c>
       <c r="H2" t="n">
-        <v>344.184</v>
+        <v>344.864</v>
       </c>
       <c r="I2" t="n">
-        <v>344.471</v>
+        <v>345.268</v>
       </c>
       <c r="J2" t="n">
         <v>11393400000</v>
